--- a/docs/요구사항_정의서_상세.xlsx
+++ b/docs/요구사항_정의서_상세.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -101,6 +101,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -481,6 +484,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,7 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -554,6 +557,11 @@
           <t>담당 파트</t>
         </is>
       </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>담당자 (R&amp;R)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -611,6 +619,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -668,6 +681,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -725,6 +743,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -782,6 +805,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -839,6 +867,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -896,6 +929,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -953,6 +991,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1010,6 +1053,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1067,6 +1115,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1124,6 +1177,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1181,6 +1239,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1238,6 +1301,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1295,6 +1363,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1352,6 +1425,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1409,6 +1487,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1466,6 +1549,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1523,6 +1611,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1580,6 +1673,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1637,6 +1735,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -1694,6 +1797,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1751,6 +1859,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -1808,6 +1921,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1865,6 +1983,11 @@
           <t>Backend / FastAPI</t>
         </is>
       </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -1922,6 +2045,11 @@
           <t>ML / FastAPI</t>
         </is>
       </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1979,6 +2107,11 @@
           <t>ML / FastAPI</t>
         </is>
       </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -2036,6 +2169,11 @@
           <t>ML / FastAPI</t>
         </is>
       </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -2093,6 +2231,11 @@
           <t>ML / FastAPI</t>
         </is>
       </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -2150,6 +2293,11 @@
           <t>Backend / ML</t>
         </is>
       </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -2207,6 +2355,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -2264,6 +2417,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -2321,6 +2479,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -2378,6 +2541,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2435,6 +2603,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -2492,6 +2665,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2549,6 +2727,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -2606,6 +2789,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -2663,6 +2851,11 @@
           <t>Frontend / Backend</t>
         </is>
       </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -2720,6 +2913,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -2777,6 +2975,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -2834,6 +3037,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -2891,6 +3099,11 @@
           <t>ML / Backend</t>
         </is>
       </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -2948,6 +3161,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -3005,6 +3223,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -3062,6 +3285,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -3119,6 +3347,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -3176,6 +3409,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -3233,6 +3471,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -3290,6 +3533,11 @@
           <t>Frontend / Backend</t>
         </is>
       </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -3347,6 +3595,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -3404,6 +3657,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -3461,6 +3719,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -3518,6 +3781,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -3575,6 +3843,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -3632,6 +3905,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -3689,6 +3967,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -3746,6 +4029,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -3803,6 +4091,11 @@
           <t>Frontend / Backend</t>
         </is>
       </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -3860,6 +4153,11 @@
           <t>Frontend</t>
         </is>
       </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -3917,6 +4215,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -3974,6 +4277,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -4031,6 +4339,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -4088,6 +4401,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -4145,6 +4463,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -4202,6 +4525,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
@@ -4259,6 +4587,11 @@
           <t>Backend / Frontend</t>
         </is>
       </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
@@ -4316,6 +4649,11 @@
           <t>Frontend / Backend</t>
         </is>
       </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 &amp; 팀원</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
@@ -4373,6 +4711,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -4430,6 +4773,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -4487,6 +4835,11 @@
           <t>Backend</t>
         </is>
       </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -4542,6 +4895,11 @@
       <c r="K74" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
         </is>
       </c>
     </row>
@@ -4556,13 +4914,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="67" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4579,7 +4938,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4601,6 +4959,11 @@
           <t>설명</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>담당자 (R&amp;R)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -4623,6 +4986,11 @@
           <t>기능 요구사항 식별자</t>
         </is>
       </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>전체 공통</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -4645,6 +5013,11 @@
           <t>회원가입, 로그인, JWT 인증, 소셜 로그인, 프로필 관리</t>
         </is>
       </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -4667,6 +5040,11 @@
           <t>반려동물 1:N 온보딩, 품종 자동완성, 프로필 관리</t>
         </is>
       </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -4689,6 +5067,11 @@
           <t>Vision AI 분석, Gemini RAG 케어 리포트 생성, 위험도 판정</t>
         </is>
       </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -4711,6 +5094,11 @@
           <t>OBSERVATION/CAUTION(타임라인) vs EMERGENCY(24시 병원) 동적 분기</t>
         </is>
       </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -4733,6 +5121,11 @@
           <t>Before/After 슬라이더 비교 및 Gemini 경과 변화 추이 소견</t>
         </is>
       </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -4755,6 +5148,11 @@
           <t>카카오/네이버 지도 API, 위치 기반 주변 24시 응급 병원 검색</t>
         </is>
       </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -4777,6 +5175,11 @@
           <t>네이버 뉴스 OpenAPI 수집 및 6시간 캐싱 스케줄러</t>
         </is>
       </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -4799,6 +5202,11 @@
           <t>AI 진단 리포트 선택 첨부 게시글 및 댓글 소통</t>
         </is>
       </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -4819,6 +5227,11 @@
       <c r="D14" s="5" t="inlineStr">
         <is>
           <t>마이페이지 대시보드, 글로벌 예외 처리, Swagger API 문서</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
         </is>
       </c>
     </row>
